--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36422.6</v>
+        <v>36091.8</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10906.22</v>
+        <v>11005.63</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10705.22</v>
+        <v>10802.8</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8407.74</v>
+        <v>8353.889999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15374.07</v>
+        <v>15739.62</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14057.76</v>
+        <v>14283.67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1078113-63-CM25</t>
+          <t>411-115-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36091.8</v>
+        <v>7130.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1078113-81-CM25</t>
+          <t>1557-115-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11005.63</v>
+        <v>12735.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1078113-82-CM25</t>
+          <t>4192-2867-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10802.8</v>
+        <v>11505.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>411-22-CM26</t>
+          <t>2380-2068-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8353.889999999999</v>
+        <v>110147.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4192-3-CM26</t>
+          <t>2380-2242-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>96.799.250-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15739.62</v>
+        <v>30283.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1729-105-CM26</t>
+          <t>1078113-63-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,311 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>36091.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1078113-81-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.510.000-7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>11005.63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1078113-82-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.510.000-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.011.398-0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>10802.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>411-22-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.251.900-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>8353.889999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4192-3-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>15739.62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1729-105-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.030.400-7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOLNET SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>14283.67</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1078113-63-CM25</t>
+          <t>411-22-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>36091.8</v>
+        <v>8353.889999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1078113-81-CM25</t>
+          <t>4192-3-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11005.63</v>
+        <v>15739.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1078113-82-CM25</t>
+          <t>1729-105-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,189 +996,6 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10802.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>411-22-CM26</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>69.251.900-0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>TCHILECOM</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>8353.889999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4192-3-CM26</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>69.030.300-0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SOLNET SPA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>15739.62</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1729-105-CM26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>69.030.400-7</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SOLNET SPA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
         <v>14283.67</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.624.276-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -636,7 +640,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4192-2867-CM25</t>
+          <t>1151575-33-SE25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +650,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>65.195.573-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +680,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>Nueva Gestión</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>76.325.497-6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11505.34</v>
+        <v>8076.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2380-2068-CM25</t>
+          <t>4192-2867-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +715,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +745,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>110147.94</v>
+        <v>11505.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2380-2242-CM25</t>
+          <t>2380-2068-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +776,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,28 +806,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30283.05</v>
+        <v>110147.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>411-22-CM26</t>
+          <t>2380-2242-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +841,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +856,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,28 +871,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8353.889999999999</v>
+        <v>30283.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4192-3-CM26</t>
+          <t>411-22-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +911,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +921,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +936,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +951,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15739.62</v>
+        <v>8353.889999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1729-105-CM26</t>
+          <t>4192-3-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +967,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +982,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,6 +1012,67 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>15739.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1729-105-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.030.400-7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>14283.67</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1076,6 +1076,71 @@
         <v>14283.67</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>751-366-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>15142.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
